--- a/backend/sample_data/timetable_slots_information.xlsx
+++ b/backend/sample_data/timetable_slots_information.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\school_timeTable\backend\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ABAC31-93E2-479F-8733-3F323648781E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F448D4-A996-48AF-87DC-3351017BAB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16905" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11895" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="10">
   <si>
     <t>Monday</t>
   </si>
@@ -40,9 +53,6 @@
     <t>morning</t>
   </si>
   <si>
-    <t>afternoon</t>
-  </si>
-  <si>
     <t>Thứ</t>
   </si>
   <si>
@@ -50,6 +60,9 @@
   </si>
   <si>
     <t>Tiết</t>
+  </si>
+  <si>
+    <t>Saturday</t>
   </si>
 </sst>
 </file>
@@ -95,7 +108,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -402,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -411,13 +424,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -477,10 +490,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -488,10 +501,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -499,10 +512,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -510,10 +523,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -521,10 +534,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -532,7 +545,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
         <v>5</v>
@@ -543,7 +556,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
         <v>5</v>
@@ -554,7 +567,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
@@ -565,7 +578,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
         <v>5</v>
@@ -576,7 +589,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
@@ -587,10 +600,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -598,10 +611,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -609,10 +622,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -620,10 +633,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -631,10 +644,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -642,7 +655,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
@@ -653,7 +666,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
@@ -664,7 +677,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
@@ -675,7 +688,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
@@ -686,7 +699,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
@@ -697,10 +710,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -708,10 +721,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -719,10 +732,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -730,10 +743,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>4</v>
@@ -741,232 +754,12 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>4</v>
-      </c>
-      <c r="B49" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51">
         <v>5</v>
       </c>
     </row>
